--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N80_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N80_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.14146677441194</v>
+        <v>6.19798835084194</v>
       </c>
       <c r="D2" t="n">
-        <v>27.419604903612</v>
+        <v>4.45568579683695</v>
       </c>
       <c r="E2" t="n">
-        <v>3.328065265069911</v>
+        <v>0.5408106055738604</v>
       </c>
       <c r="F2" t="n">
-        <v>5.716933097560137</v>
+        <v>0.9290016283535223</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.48533624427212</v>
+        <v>5.116367139694219</v>
       </c>
       <c r="D3" t="n">
-        <v>15.98573870849173</v>
+        <v>2.597682540129906</v>
       </c>
       <c r="E3" t="n">
-        <v>3.328065265069911</v>
+        <v>0.5408106055738604</v>
       </c>
       <c r="F3" t="n">
-        <v>5.716933097560137</v>
+        <v>0.9290016283535223</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
